--- a/ai-engine/output/output_results.xlsx
+++ b/ai-engine/output/output_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,30 +506,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>anomaly_flag</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rule_status</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rule_reason</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>final_status</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>risk_score</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>risk_reason</t>
         </is>
@@ -537,37 +542,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B2" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>33.71</v>
+        <v>24.83</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>160</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>90</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -576,35 +581,38 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6932793308475265</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ML Decision</t>
+          <t>DANGER</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>27</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Safe Conditions</t>
+          <t>High Water Level</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>72</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Moderate Gas, Moderate Gas Range, High Water</t>
         </is>
       </c>
     </row>

--- a/ai-engine/output/output_results.xlsx
+++ b/ai-engine/output/output_results.xlsx
@@ -542,13 +542,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>19.2</v>
+        <v>20.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -560,19 +560,19 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6932793308475265</v>
+        <v>0.9442458069842522</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -594,25 +594,25 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>DANGER</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>High Water Level</t>
+          <t>ML Decision</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Moderate Gas, Moderate Gas Range, High Water</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>

--- a/ai-engine/output/output_results.xlsx
+++ b/ai-engine/output/output_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,21 @@
           <t>risk_reason</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>entry_decision</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>safe_work_time_minutes</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>decision_reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -554,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>24.83</v>
+        <v>33.88</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -613,6 +628,19 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>Normal</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ALLOW</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Safe working conditions</t>
         </is>
       </c>
     </row>
